--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,148 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="E7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>5400</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,37 +885,61 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2500</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +967,26 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -879,25 +997,43 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>50400</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +1061,26 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +1089,108 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>500</v>
+        <v>10800</v>
       </c>
       <c r="E17" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>62800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-5400</v>
       </c>
       <c r="E18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,66 +1202,108 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>800</v>
       </c>
       <c r="E20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G20" s="3">
+        <v>200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-4700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,37 +1331,73 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="E23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1131,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1143,16 +1417,34 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1472,120 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="E26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="E27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1613,26 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1660,26 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1707,26 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1754,120 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="E33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1895,125 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="E35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="E38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +2025,14 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,57 +2044,81 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
-        <v>200</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>50100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>51600</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
+        <v>20200</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1588,37 +2126,73 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,153 +2220,261 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>400</v>
+        <v>57700</v>
       </c>
       <c r="E46" s="3">
+        <v>59700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>64700</v>
+      </c>
+      <c r="G46" s="3">
+        <v>68900</v>
+      </c>
+      <c r="H46" s="3">
+        <v>73600</v>
+      </c>
+      <c r="I46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="L46" s="3">
         <v>600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="M46" s="3">
         <v>700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="N46" s="3">
         <v>200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>116800</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>116300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="L47" s="3">
         <v>116200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="M47" s="3">
         <v>116200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>23200</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>23700</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>24700</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2502,26 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2549,73 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>2600</v>
       </c>
       <c r="E52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2643,73 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>117200</v>
+        <v>85000</v>
       </c>
       <c r="E54" s="3">
+        <v>87700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>92400</v>
+      </c>
+      <c r="G54" s="3">
+        <v>97200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>102500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="J54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="K54" s="3">
         <v>116800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="L54" s="3">
         <v>116900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="M54" s="3">
         <v>117000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="N54" s="3">
         <v>200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="O54" s="3">
         <v>100</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2721,14 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2740,296 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
+        <v>700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>10500</v>
       </c>
       <c r="E59" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3100</v>
+        <v>14500</v>
       </c>
       <c r="E60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="H60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="L62" s="3">
         <v>4000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="G62" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +3057,26 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +3104,26 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +3151,73 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7200</v>
+        <v>16400</v>
       </c>
       <c r="E66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>18100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H66" s="3">
+        <v>19600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K66" s="3">
         <v>6700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="L66" s="3">
         <v>4700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="M66" s="3">
         <v>4100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +3229,14 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +3264,26 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +3311,26 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +3358,26 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +3405,73 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-6700</v>
+        <v>-188800</v>
       </c>
       <c r="E72" s="3">
+        <v>-184200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-180900</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-173700</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-168000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="L72" s="3">
         <v>-3900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="M72" s="3">
         <v>-3200</v>
       </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +3499,26 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +3546,26 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +3593,73 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>74200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>77800</v>
+      </c>
+      <c r="H76" s="3">
+        <v>82900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="K76" s="3">
         <v>110100</v>
       </c>
-      <c r="E76" s="3">
-        <v>110100</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="L76" s="3">
         <v>112200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="M76" s="3">
         <v>112900</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +3687,125 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="E80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-4600</v>
       </c>
       <c r="E81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3817,61 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3899,26 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3946,26 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3993,26 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +4040,26 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +4087,73 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>-1700</v>
       </c>
       <c r="E89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,8 +4165,14 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2876,8 +4200,26 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +4247,26 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +4294,73 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G94" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-116200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +4372,14 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +4407,26 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +4454,26 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +4501,26 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +4548,73 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>73400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="M100" s="3">
         <v>117100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3133,50 +4625,86 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-7900</v>
       </c>
       <c r="E102" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>40300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E8" s="3">
         <v>5400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5100</v>
       </c>
       <c r="G8" s="3">
         <v>5100</v>
       </c>
       <c r="H8" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="I8" s="3">
         <v>4800</v>
       </c>
       <c r="J8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K8" s="3">
         <v>4700</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
@@ -778,8 +782,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -790,23 +797,23 @@
         <v>2000</v>
       </c>
       <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2000</v>
       </c>
       <c r="I9" s="3">
         <v>2000</v>
       </c>
       <c r="J9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K9" s="3">
         <v>2100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -825,35 +832,38 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2800</v>
       </c>
       <c r="I10" s="3">
         <v>2800</v>
       </c>
       <c r="J10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K10" s="3">
         <v>2600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,19 +904,20 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E12" s="3">
         <v>2500</v>
       </c>
       <c r="F12" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G12" s="3">
         <v>3000</v>
@@ -912,14 +926,14 @@
         <v>3000</v>
       </c>
       <c r="I12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J12" s="3">
         <v>2600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2500</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,35 +1002,38 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>50400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1032,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E17" s="3">
         <v>10800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>62800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-58000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,38 +1241,39 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1249,41 +1283,44 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-48600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1339,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-49300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1405,25 +1451,25 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-49300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-49300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,38 +1839,41 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1813,61 +1883,67 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-49300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-49300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,44 +2136,45 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46800</v>
-      </c>
-      <c r="I41" s="3">
-        <v>6500</v>
       </c>
       <c r="J41" s="3">
         <v>6500</v>
       </c>
       <c r="K41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,31 +2184,34 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E42" s="3">
         <v>37500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>51600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20200</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2144,34 +2234,37 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>3200</v>
       </c>
       <c r="J43" s="3">
         <v>3200</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2191,8 +2284,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,25 +2334,28 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3300</v>
       </c>
       <c r="I45" s="3">
         <v>3300</v>
@@ -2265,75 +2364,81 @@
         <v>3300</v>
       </c>
       <c r="K45" s="3">
-        <v>300</v>
+        <v>3300</v>
       </c>
       <c r="L45" s="3">
         <v>300</v>
       </c>
       <c r="M45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E46" s="3">
         <v>57700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>64700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>68900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73600</v>
-      </c>
-      <c r="I46" s="3">
-        <v>13000</v>
       </c>
       <c r="J46" s="3">
         <v>13000</v>
       </c>
       <c r="K46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L46" s="3">
         <v>500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2359,16 +2464,16 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>116300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>116200</v>
       </c>
       <c r="M47" s="3">
         <v>116200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>116200</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2379,34 +2484,37 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2200</v>
       </c>
       <c r="J48" s="3">
         <v>2200</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2426,34 +2534,37 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E49" s="3">
         <v>22800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24700</v>
-      </c>
-      <c r="I49" s="3">
-        <v>25100</v>
       </c>
       <c r="J49" s="3">
         <v>25100</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,44 +2684,47 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="E52" s="3">
         <v>2600</v>
       </c>
       <c r="F52" s="3">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="G52" s="3">
         <v>2200</v>
       </c>
       <c r="H52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I52" s="3">
         <v>2300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1600</v>
       </c>
       <c r="J52" s="3">
         <v>1600</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E54" s="3">
         <v>85000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>92400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>97200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>102500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>41800</v>
       </c>
       <c r="J54" s="3">
         <v>41800</v>
       </c>
       <c r="K54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="L54" s="3">
         <v>116800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>117000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,8 +2876,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2755,25 +2886,25 @@
         <v>3500</v>
       </c>
       <c r="E57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3200</v>
       </c>
       <c r="J57" s="3">
         <v>3200</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2793,8 +2924,11 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2802,84 +2936,87 @@
         <v>500</v>
       </c>
       <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
-      </c>
-      <c r="F58" s="3">
-        <v>700</v>
       </c>
       <c r="G58" s="3">
         <v>700</v>
       </c>
       <c r="H58" s="3">
+        <v>700</v>
+      </c>
+      <c r="I58" s="3">
         <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>3100</v>
       </c>
       <c r="J58" s="3">
         <v>3100</v>
       </c>
       <c r="K58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E59" s="3">
         <v>10500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>10700</v>
       </c>
       <c r="J59" s="3">
         <v>10700</v>
       </c>
       <c r="K59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="L59" s="3">
         <v>1700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>100</v>
       </c>
       <c r="M59" s="3">
         <v>100</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
@@ -2887,81 +3024,87 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>17100</v>
       </c>
       <c r="J60" s="3">
         <v>17100</v>
       </c>
       <c r="K60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>700</v>
-      </c>
-      <c r="F61" s="3">
-        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>200</v>
       </c>
       <c r="H61" s="3">
+        <v>200</v>
+      </c>
+      <c r="I61" s="3">
         <v>300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>400</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2981,34 +3124,37 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2700</v>
       </c>
       <c r="J62" s="3">
         <v>2700</v>
       </c>
       <c r="K62" s="3">
-        <v>4000</v>
+        <v>2700</v>
       </c>
       <c r="L62" s="3">
         <v>4000</v>
@@ -3016,8 +3162,8 @@
       <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>4000</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3028,8 +3174,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E66" s="3">
         <v>16400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>20100</v>
       </c>
       <c r="J66" s="3">
         <v>20100</v>
       </c>
       <c r="K66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-188800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-184200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-180900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-173700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-168000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-118700</v>
       </c>
       <c r="J72" s="3">
         <v>-118700</v>
       </c>
       <c r="K72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="L72" s="3">
         <v>-6200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3200</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
       <c r="O72" s="3">
         <v>0</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E76" s="3">
         <v>68600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>77800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>82900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>21700</v>
       </c>
       <c r="J76" s="3">
         <v>21700</v>
       </c>
       <c r="K76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="L76" s="3">
         <v>110100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>112200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112900</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
       <c r="O76" s="3">
         <v>0</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-49300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,8 +4021,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3841,7 +4040,7 @@
         <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
@@ -3850,7 +4049,7 @@
         <v>600</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3870,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-600</v>
       </c>
       <c r="L89" s="3">
         <v>-600</v>
       </c>
       <c r="M89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,44 +4539,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>18100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-116200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4359,8 +4589,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,44 +4809,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
         <v>73400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>500</v>
       </c>
       <c r="L100" s="3">
         <v>500</v>
       </c>
       <c r="M100" s="3">
+        <v>500</v>
+      </c>
+      <c r="N100" s="3">
         <v>117100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4613,8 +4859,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4625,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
@@ -4634,14 +4883,14 @@
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-37500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-100</v>
       </c>
       <c r="L102" s="3">
         <v>-100</v>
       </c>
       <c r="M102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,117 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E8" s="3">
         <v>5700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5100</v>
       </c>
       <c r="H8" s="3">
         <v>5100</v>
       </c>
       <c r="I8" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="J8" s="3">
         <v>4800</v>
       </c>
       <c r="K8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L8" s="3">
         <v>4700</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -785,13 +789,16 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="E9" s="3">
         <v>2000</v>
@@ -800,23 +807,23 @@
         <v>2000</v>
       </c>
       <c r="G9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="3">
         <v>2300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2000</v>
       </c>
       <c r="J9" s="3">
         <v>2000</v>
       </c>
       <c r="K9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L9" s="3">
         <v>2100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,38 +842,41 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2800</v>
       </c>
       <c r="J10" s="3">
         <v>2800</v>
       </c>
       <c r="K10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L10" s="3">
         <v>2600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,22 +918,23 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="3">
         <v>2400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2500</v>
       </c>
       <c r="F12" s="3">
         <v>2500</v>
       </c>
       <c r="G12" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="H12" s="3">
         <v>3000</v>
@@ -929,14 +943,14 @@
         <v>3000</v>
       </c>
       <c r="J12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K12" s="3">
         <v>2600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2500</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,38 +1022,41 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>45100</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
-        <v>50400</v>
+        <v>46100</v>
       </c>
       <c r="J14" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1055,31 +1075,34 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10800</v>
       </c>
-      <c r="F17" s="3">
-        <v>9900</v>
-      </c>
       <c r="G17" s="3">
-        <v>14400</v>
+        <v>11500</v>
       </c>
       <c r="H17" s="3">
-        <v>11000</v>
+        <v>13500</v>
       </c>
       <c r="I17" s="3">
-        <v>62800</v>
+        <v>11600</v>
       </c>
       <c r="J17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K17" s="3">
         <v>13700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
         <v>0</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4500</v>
+        <v>-4900</v>
       </c>
       <c r="E18" s="3">
-        <v>-5400</v>
+        <v>-4600</v>
       </c>
       <c r="F18" s="3">
-        <v>-4600</v>
+        <v>-5500</v>
       </c>
       <c r="G18" s="3">
-        <v>-9300</v>
+        <v>-6200</v>
       </c>
       <c r="H18" s="3">
-        <v>-5900</v>
+        <v>-8400</v>
       </c>
       <c r="I18" s="3">
-        <v>-58000</v>
+        <v>-6500</v>
       </c>
       <c r="J18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-8900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+      <c r="Q18" s="3">
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,41 +1275,42 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-800</v>
+        <v>-1500</v>
       </c>
       <c r="E20" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="F20" s="3">
-        <v>1100</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>2200</v>
+        <v>-47200</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>-1600</v>
       </c>
       <c r="I20" s="3">
-        <v>8700</v>
+        <v>-46200</v>
       </c>
       <c r="J20" s="3">
+        <v>38800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1286,44 +1320,47 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4600</v>
+        <v>-2600</v>
       </c>
       <c r="E21" s="3">
-        <v>-3900</v>
+        <v>-5200</v>
       </c>
       <c r="F21" s="3">
-        <v>-2800</v>
+        <v>-4500</v>
       </c>
       <c r="G21" s="3">
-        <v>-6400</v>
+        <v>41000</v>
       </c>
       <c r="H21" s="3">
-        <v>-5000</v>
+        <v>-6100</v>
       </c>
       <c r="I21" s="3">
-        <v>-48600</v>
+        <v>40300</v>
       </c>
       <c r="J21" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-8400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1351,22 +1391,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1392,58 +1432,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1454,25 +1500,25 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
-        <v>-3300</v>
-      </c>
       <c r="G27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H27" s="3">
         <v>-7200</v>
       </c>
-      <c r="H27" s="3">
-        <v>-5700</v>
-      </c>
       <c r="I27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-49300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,41 +1909,44 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="F32" s="3">
-        <v>-1100</v>
+        <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>-2200</v>
+        <v>47200</v>
       </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>1600</v>
       </c>
       <c r="I32" s="3">
-        <v>-8700</v>
+        <v>46200</v>
       </c>
       <c r="J32" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -1886,64 +1956,70 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-49300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-49300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,47 +2223,48 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E41" s="3">
         <v>21000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46800</v>
-      </c>
-      <c r="J41" s="3">
-        <v>6500</v>
       </c>
       <c r="K41" s="3">
         <v>6500</v>
       </c>
       <c r="L41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,34 +2274,37 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E42" s="3">
         <v>26400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>37500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>50100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>51600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>20200</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2237,37 +2327,40 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E43" s="3">
         <v>4200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I43" s="3">
         <v>4500</v>
       </c>
-      <c r="G43" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H43" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3300</v>
-      </c>
-      <c r="J43" s="3">
-        <v>3200</v>
       </c>
       <c r="K43" s="3">
         <v>3200</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2287,31 +2380,34 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2337,28 +2433,31 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3300</v>
       </c>
       <c r="J45" s="3">
         <v>3300</v>
@@ -2367,116 +2466,122 @@
         <v>3300</v>
       </c>
       <c r="L45" s="3">
-        <v>300</v>
+        <v>3300</v>
       </c>
       <c r="M45" s="3">
         <v>300</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E46" s="3">
         <v>55400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>59700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>64700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>68900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73600</v>
-      </c>
-      <c r="J46" s="3">
-        <v>13000</v>
       </c>
       <c r="K46" s="3">
         <v>13000</v>
       </c>
       <c r="L46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M46" s="3">
         <v>500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>116300</v>
-      </c>
-      <c r="M47" s="3">
-        <v>116200</v>
       </c>
       <c r="N47" s="3">
         <v>116200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>116200</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2487,37 +2592,40 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2200</v>
       </c>
       <c r="K48" s="3">
         <v>2200</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2537,37 +2645,40 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E49" s="3">
         <v>22300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>25100</v>
       </c>
       <c r="K49" s="3">
         <v>25100</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,47 +2804,50 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2700</v>
+        <v>1600</v>
       </c>
       <c r="E52" s="3">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="F52" s="3">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="G52" s="3">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="H52" s="3">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="I52" s="3">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="J52" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="K52" s="3">
         <v>1600</v>
       </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
       </c>
       <c r="N52" s="3">
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E54" s="3">
         <v>82200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>92400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>102500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>41800</v>
       </c>
       <c r="K54" s="3">
         <v>41800</v>
       </c>
       <c r="L54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="M54" s="3">
         <v>116800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>117000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,37 +3007,38 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="E57" s="3">
         <v>3500</v>
       </c>
       <c r="F57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>3200</v>
       </c>
       <c r="K57" s="3">
         <v>3200</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2927,99 +3058,105 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
         <v>500</v>
       </c>
       <c r="F58" s="3">
+        <v>500</v>
+      </c>
+      <c r="G58" s="3">
         <v>600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>700</v>
       </c>
       <c r="H58" s="3">
         <v>700</v>
       </c>
       <c r="I58" s="3">
+        <v>700</v>
+      </c>
+      <c r="J58" s="3">
         <v>600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>3100</v>
       </c>
       <c r="K58" s="3">
         <v>3100</v>
       </c>
       <c r="L58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11900</v>
+        <v>5500</v>
       </c>
       <c r="E59" s="3">
-        <v>10500</v>
+        <v>6400</v>
       </c>
       <c r="F59" s="3">
-        <v>8500</v>
+        <v>5600</v>
       </c>
       <c r="G59" s="3">
-        <v>10600</v>
+        <v>6000</v>
       </c>
       <c r="H59" s="3">
-        <v>9800</v>
+        <v>4700</v>
       </c>
       <c r="I59" s="3">
-        <v>8900</v>
+        <v>3500</v>
       </c>
       <c r="J59" s="3">
-        <v>10700</v>
+        <v>3300</v>
       </c>
       <c r="K59" s="3">
         <v>10700</v>
       </c>
       <c r="L59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="M59" s="3">
         <v>1700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>100</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3027,58 +3164,64 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E60" s="3">
         <v>16000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>17100</v>
       </c>
       <c r="K60" s="3">
         <v>17100</v>
       </c>
       <c r="L60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3086,28 +3229,28 @@
         <v>500</v>
       </c>
       <c r="E61" s="3">
+        <v>500</v>
+      </c>
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>700</v>
-      </c>
-      <c r="G61" s="3">
-        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>200</v>
       </c>
       <c r="I61" s="3">
+        <v>200</v>
+      </c>
+      <c r="J61" s="3">
         <v>300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>400</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3127,37 +3270,40 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1300</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>3400</v>
+        <v>1500</v>
       </c>
       <c r="H62" s="3">
-        <v>5200</v>
+        <v>2400</v>
       </c>
       <c r="I62" s="3">
-        <v>5700</v>
+        <v>4000</v>
       </c>
       <c r="J62" s="3">
-        <v>2700</v>
+        <v>4400</v>
       </c>
       <c r="K62" s="3">
         <v>2700</v>
       </c>
       <c r="L62" s="3">
-        <v>4000</v>
+        <v>2700</v>
       </c>
       <c r="M62" s="3">
         <v>4000</v>
@@ -3165,8 +3311,8 @@
       <c r="N62" s="3">
         <v>4000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>4000</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E66" s="3">
         <v>17800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>20100</v>
       </c>
       <c r="K66" s="3">
         <v>20100</v>
       </c>
       <c r="L66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="M66" s="3">
         <v>6700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-194100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-188800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-184200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-180900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-173700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-168000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-118700</v>
       </c>
       <c r="K72" s="3">
         <v>-118700</v>
       </c>
       <c r="L72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="M72" s="3">
         <v>-6200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3200</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E76" s="3">
         <v>64300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>68600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>77800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>82900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>21700</v>
       </c>
       <c r="K76" s="3">
         <v>21700</v>
       </c>
       <c r="L76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="M76" s="3">
         <v>110100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>112900</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
       <c r="P76" s="3">
         <v>0</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-49300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4034,25 +4233,25 @@
         <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-600</v>
       </c>
       <c r="M89" s="3">
         <v>-600</v>
       </c>
       <c r="N89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,47 +4769,50 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>11500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>18100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-116200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,31 +4845,32 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,8 +5055,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4821,38 +5067,38 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>73400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
-      </c>
-      <c r="L100" s="3">
-        <v>500</v>
       </c>
       <c r="M100" s="3">
         <v>500</v>
       </c>
       <c r="N100" s="3">
+        <v>500</v>
+      </c>
+      <c r="O100" s="3">
         <v>117100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4862,38 +5108,41 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>8700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3100</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-100</v>
       </c>
       <c r="M102" s="3">
         <v>-100</v>
       </c>
       <c r="N102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,124 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E8" s="3">
         <v>6200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5100</v>
       </c>
       <c r="I8" s="3">
         <v>5100</v>
       </c>
       <c r="J8" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="K8" s="3">
         <v>4800</v>
       </c>
       <c r="L8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M8" s="3">
         <v>4700</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -792,16 +795,19 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2000</v>
       </c>
       <c r="F9" s="3">
         <v>2000</v>
@@ -810,23 +816,23 @@
         <v>2000</v>
       </c>
       <c r="H9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>2000</v>
       </c>
       <c r="K9" s="3">
         <v>2000</v>
       </c>
       <c r="L9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M9" s="3">
         <v>2100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,41 +851,44 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E10" s="3">
         <v>4000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2800</v>
       </c>
       <c r="K10" s="3">
         <v>2800</v>
       </c>
       <c r="L10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M10" s="3">
         <v>2600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,25 +931,26 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E12" s="3">
         <v>2600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2500</v>
       </c>
       <c r="G12" s="3">
         <v>2500</v>
       </c>
       <c r="H12" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I12" s="3">
         <v>3000</v>
@@ -946,14 +959,14 @@
         <v>3000</v>
       </c>
       <c r="K12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L12" s="3">
         <v>2600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2500</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1041,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1039,27 +1058,27 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>45100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>46100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1078,35 +1097,38 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>700</v>
       </c>
       <c r="F15" s="3">
         <v>700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
       </c>
       <c r="J15" s="3">
+        <v>700</v>
+      </c>
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1131,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1174,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E17" s="3">
         <v>11000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
+      <c r="R18" s="3">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,44 +1308,45 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-47200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-46200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>38800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1323,47 +1356,50 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-45700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1418,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1409,7 +1448,7 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1435,66 +1474,72 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1503,25 +1548,25 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1541,8 +1586,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-49300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,44 +1978,47 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>47200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>46200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-38800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -1959,67 +2028,73 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-49300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-49300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,50 +2309,51 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E41" s="3">
         <v>14600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46800</v>
-      </c>
-      <c r="K41" s="3">
-        <v>6500</v>
       </c>
       <c r="L41" s="3">
         <v>6500</v>
       </c>
       <c r="M41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2277,37 +2363,40 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E42" s="3">
         <v>26800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>37500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>51600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2330,40 +2419,43 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>3200</v>
       </c>
       <c r="L43" s="3">
         <v>3200</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2383,8 +2475,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2409,8 +2504,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2436,8 +2531,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2445,22 +2543,22 @@
         <v>4500</v>
       </c>
       <c r="E45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F45" s="3">
         <v>3800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3300</v>
       </c>
       <c r="K45" s="3">
         <v>3300</v>
@@ -2469,81 +2567,87 @@
         <v>3300</v>
       </c>
       <c r="M45" s="3">
-        <v>300</v>
+        <v>3300</v>
       </c>
       <c r="N45" s="3">
         <v>300</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
       <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E46" s="3">
         <v>50200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>68900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>73600</v>
-      </c>
-      <c r="K46" s="3">
-        <v>13000</v>
       </c>
       <c r="L46" s="3">
         <v>13000</v>
       </c>
       <c r="M46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N46" s="3">
         <v>500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2568,23 +2672,23 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>116300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>116200</v>
       </c>
       <c r="O47" s="3">
         <v>116200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>116200</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2595,40 +2699,43 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2200</v>
       </c>
       <c r="L48" s="3">
         <v>2200</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2648,40 +2755,43 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E49" s="3">
         <v>27900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24700</v>
-      </c>
-      <c r="K49" s="3">
-        <v>25100</v>
       </c>
       <c r="L49" s="3">
         <v>25100</v>
       </c>
       <c r="M49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2701,8 +2811,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,8 +2923,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2831,26 +2950,26 @@
         <v>1600</v>
       </c>
       <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>1600</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3035,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E54" s="3">
         <v>82700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>85000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>87700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>102500</v>
-      </c>
-      <c r="K54" s="3">
-        <v>41800</v>
       </c>
       <c r="L54" s="3">
         <v>41800</v>
       </c>
       <c r="M54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="N54" s="3">
         <v>116800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>116900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>117000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,40 +3137,41 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3500</v>
       </c>
       <c r="F57" s="3">
         <v>3500</v>
       </c>
       <c r="G57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3200</v>
       </c>
       <c r="L57" s="3">
         <v>3200</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -3061,105 +3191,111 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>500</v>
       </c>
       <c r="F58" s="3">
         <v>500</v>
       </c>
       <c r="G58" s="3">
+        <v>500</v>
+      </c>
+      <c r="H58" s="3">
         <v>600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>700</v>
       </c>
       <c r="J58" s="3">
+        <v>700</v>
+      </c>
+      <c r="K58" s="3">
         <v>600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3100</v>
       </c>
       <c r="L58" s="3">
         <v>3100</v>
       </c>
       <c r="M58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
         <v>5500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>10700</v>
       </c>
       <c r="L59" s="3">
         <v>10700</v>
       </c>
       <c r="M59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="N59" s="3">
         <v>1700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>100</v>
       </c>
       <c r="O59" s="3">
         <v>100</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3167,8 +3303,11 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3176,84 +3315,87 @@
         <v>17300</v>
       </c>
       <c r="E60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F60" s="3">
         <v>16000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13700</v>
-      </c>
-      <c r="K60" s="3">
-        <v>17100</v>
       </c>
       <c r="L60" s="3">
         <v>17100</v>
       </c>
       <c r="M60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
         <v>500</v>
       </c>
       <c r="F61" s="3">
+        <v>500</v>
+      </c>
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
-      </c>
-      <c r="H61" s="3">
-        <v>200</v>
       </c>
       <c r="I61" s="3">
         <v>200</v>
       </c>
       <c r="J61" s="3">
+        <v>200</v>
+      </c>
+      <c r="K61" s="3">
         <v>300</v>
-      </c>
-      <c r="K61" s="3">
-        <v>400</v>
       </c>
       <c r="L61" s="3">
         <v>400</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3273,8 +3415,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3284,29 +3429,29 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>1500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4400</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2700</v>
       </c>
       <c r="L62" s="3">
         <v>2700</v>
       </c>
       <c r="M62" s="3">
-        <v>4000</v>
+        <v>2700</v>
       </c>
       <c r="N62" s="3">
         <v>4000</v>
@@ -3314,8 +3459,8 @@
       <c r="O62" s="3">
         <v>4000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>4000</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3326,8 +3471,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3639,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E66" s="3">
         <v>19100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>20100</v>
       </c>
       <c r="L66" s="3">
         <v>20100</v>
       </c>
       <c r="M66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="N66" s="3">
         <v>6700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3941,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-206700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-196800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-194100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-188800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-184200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-180900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-173700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-168000</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-118700</v>
       </c>
       <c r="L72" s="3">
         <v>-118700</v>
       </c>
       <c r="M72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="N72" s="3">
         <v>-6200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3200</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4165,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E76" s="3">
         <v>63600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>68600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>74200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>77800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>82900</v>
-      </c>
-      <c r="K76" s="3">
-        <v>21700</v>
       </c>
       <c r="L76" s="3">
         <v>21700</v>
       </c>
       <c r="M76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="N76" s="3">
         <v>110100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>112200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>112900</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
       <c r="Q76" s="3">
         <v>0</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-49300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
         <v>0</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4418,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4233,7 +4431,7 @@
         <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -4245,16 +4443,16 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4274,8 +4472,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-600</v>
       </c>
       <c r="N89" s="3">
         <v>-600</v>
       </c>
       <c r="O89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4832,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4666,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,50 +4998,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-116200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +5054,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4872,8 +5105,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4899,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,50 +5300,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
         <v>73400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>500</v>
       </c>
       <c r="N100" s="3">
         <v>500</v>
       </c>
       <c r="O100" s="3">
+        <v>500</v>
+      </c>
+      <c r="P100" s="3">
         <v>117100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5111,13 +5356,16 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
@@ -5126,26 +5374,26 @@
         <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
@@ -5164,57 +5412,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-37500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-100</v>
       </c>
       <c r="N102" s="3">
         <v>-100</v>
       </c>
       <c r="O102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,130 +656,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E8" s="3">
         <v>6600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5100</v>
       </c>
       <c r="J8" s="3">
         <v>5100</v>
       </c>
       <c r="K8" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="L8" s="3">
         <v>4800</v>
       </c>
       <c r="M8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="N8" s="3">
         <v>4700</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
@@ -798,19 +802,22 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2000</v>
       </c>
       <c r="G9" s="3">
         <v>2000</v>
@@ -819,23 +826,23 @@
         <v>2000</v>
       </c>
       <c r="I9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2000</v>
       </c>
       <c r="L9" s="3">
         <v>2000</v>
       </c>
       <c r="M9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N9" s="3">
         <v>2100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,44 +861,47 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2800</v>
       </c>
       <c r="L10" s="3">
         <v>2800</v>
       </c>
       <c r="M10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N10" s="3">
         <v>2600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,28 +945,29 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2500</v>
       </c>
       <c r="H12" s="3">
         <v>2500</v>
       </c>
       <c r="I12" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="J12" s="3">
         <v>3000</v>
@@ -962,14 +976,14 @@
         <v>3000</v>
       </c>
       <c r="L12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M12" s="3">
         <v>2600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2500</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,16 +1061,19 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>3300</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1061,27 +1081,27 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>45100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>46100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1100,8 +1120,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1109,29 +1132,29 @@
         <v>900</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>700</v>
       </c>
       <c r="G15" s="3">
         <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>700</v>
       </c>
       <c r="K15" s="3">
+        <v>700</v>
+      </c>
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1156,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14600</v>
+        <v>11600</v>
       </c>
       <c r="E17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F17" s="3">
         <v>11000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-8000</v>
+        <v>-4700</v>
       </c>
       <c r="E18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
+      <c r="S18" s="3">
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,47 +1342,48 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-47200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-46200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>38800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1359,50 +1393,53 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8600</v>
+        <v>-3400</v>
       </c>
       <c r="E21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>40300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-45700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4700</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,19 +1458,22 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1451,7 +1491,7 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1477,73 +1517,79 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-49300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1551,25 +1597,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-49300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-49300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,47 +2048,50 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>47200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>46200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-38800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2031,70 +2101,76 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-49300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-49300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,53 +2396,54 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E41" s="3">
         <v>10100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46800</v>
-      </c>
-      <c r="L41" s="3">
-        <v>6500</v>
       </c>
       <c r="M41" s="3">
         <v>6500</v>
       </c>
       <c r="N41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,40 +2453,43 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>27200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>37500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>50100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>51600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>20200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2422,43 +2512,46 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4300</v>
+        <v>5500</v>
       </c>
       <c r="E43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F43" s="3">
         <v>4400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3300</v>
-      </c>
-      <c r="L43" s="3">
-        <v>3200</v>
       </c>
       <c r="M43" s="3">
         <v>3200</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2478,8 +2571,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2507,8 +2603,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2534,34 +2630,37 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="E45" s="3">
         <v>4500</v>
       </c>
       <c r="F45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3300</v>
       </c>
       <c r="L45" s="3">
         <v>3300</v>
@@ -2570,84 +2669,90 @@
         <v>3300</v>
       </c>
       <c r="N45" s="3">
-        <v>300</v>
+        <v>3300</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E46" s="3">
         <v>46100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>55400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>57700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>59700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>64700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>68900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>73600</v>
-      </c>
-      <c r="L46" s="3">
-        <v>13000</v>
       </c>
       <c r="M46" s="3">
         <v>13000</v>
       </c>
       <c r="N46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O46" s="3">
         <v>500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2675,23 +2780,23 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>116300</v>
-      </c>
-      <c r="O47" s="3">
-        <v>116200</v>
       </c>
       <c r="P47" s="3">
         <v>116200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>116200</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2702,43 +2807,46 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>2200</v>
       </c>
       <c r="M48" s="3">
         <v>2200</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2758,43 +2866,46 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E49" s="3">
         <v>23900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24700</v>
-      </c>
-      <c r="L49" s="3">
-        <v>25100</v>
       </c>
       <c r="M49" s="3">
         <v>25100</v>
       </c>
       <c r="N49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,8 +3043,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2953,26 +3073,26 @@
         <v>1600</v>
       </c>
       <c r="K52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L52" s="3">
         <v>1700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1600</v>
       </c>
       <c r="M52" s="3">
         <v>1600</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E54" s="3">
         <v>73800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>85000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>87700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>92400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>102500</v>
-      </c>
-      <c r="L54" s="3">
-        <v>41800</v>
       </c>
       <c r="M54" s="3">
         <v>41800</v>
       </c>
       <c r="N54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="O54" s="3">
         <v>116800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>116900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>117000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,43 +3268,44 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3500</v>
       </c>
       <c r="G57" s="3">
         <v>3500</v>
       </c>
       <c r="H57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>3200</v>
       </c>
       <c r="M57" s="3">
         <v>3200</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -3194,111 +3325,117 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>500</v>
       </c>
       <c r="G58" s="3">
         <v>500</v>
       </c>
       <c r="H58" s="3">
+        <v>500</v>
+      </c>
+      <c r="I58" s="3">
         <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>700</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
       </c>
       <c r="K58" s="3">
+        <v>700</v>
+      </c>
+      <c r="L58" s="3">
         <v>600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3100</v>
       </c>
       <c r="M58" s="3">
         <v>3100</v>
       </c>
       <c r="N58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F59" s="3">
         <v>5500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5600</v>
       </c>
-      <c r="H59" s="3">
-        <v>6000</v>
-      </c>
       <c r="I59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J59" s="3">
         <v>4700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>10700</v>
       </c>
       <c r="M59" s="3">
         <v>10700</v>
       </c>
       <c r="N59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="O59" s="3">
         <v>1700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>100</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3306,99 +3443,105 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>17300</v>
+        <v>19300</v>
       </c>
       <c r="E60" s="3">
         <v>17300</v>
       </c>
       <c r="F60" s="3">
+        <v>17300</v>
+      </c>
+      <c r="G60" s="3">
         <v>16000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14500</v>
       </c>
-      <c r="H60" s="3">
-        <v>12200</v>
-      </c>
       <c r="I60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J60" s="3">
         <v>14500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13700</v>
-      </c>
-      <c r="L60" s="3">
-        <v>17100</v>
       </c>
       <c r="M60" s="3">
         <v>17100</v>
       </c>
       <c r="N60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
-      </c>
-      <c r="E61" s="3">
-        <v>500</v>
       </c>
       <c r="F61" s="3">
         <v>500</v>
       </c>
       <c r="G61" s="3">
+        <v>500</v>
+      </c>
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>700</v>
-      </c>
-      <c r="I61" s="3">
-        <v>200</v>
       </c>
       <c r="J61" s="3">
         <v>200</v>
       </c>
       <c r="K61" s="3">
+        <v>200</v>
+      </c>
+      <c r="L61" s="3">
         <v>300</v>
-      </c>
-      <c r="L61" s="3">
-        <v>400</v>
       </c>
       <c r="M61" s="3">
         <v>400</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3418,8 +3561,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3432,29 +3578,29 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>2400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4400</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2700</v>
       </c>
       <c r="M62" s="3">
         <v>2700</v>
       </c>
       <c r="N62" s="3">
-        <v>4000</v>
+        <v>2700</v>
       </c>
       <c r="O62" s="3">
         <v>4000</v>
@@ -3462,8 +3608,8 @@
       <c r="P62" s="3">
         <v>4000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>4000</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3474,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E66" s="3">
         <v>18900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>20100</v>
       </c>
       <c r="M66" s="3">
         <v>20100</v>
       </c>
       <c r="N66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="O66" s="3">
         <v>6700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-211200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-206700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-196800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-194100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-188800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-184200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-180900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-173700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-168000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-118700</v>
       </c>
       <c r="M72" s="3">
         <v>-118700</v>
       </c>
       <c r="N72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="O72" s="3">
         <v>-6200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E76" s="3">
         <v>54900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>63600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>68600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>77800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>82900</v>
-      </c>
-      <c r="L76" s="3">
-        <v>21700</v>
       </c>
       <c r="M76" s="3">
         <v>21700</v>
       </c>
       <c r="N76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="O76" s="3">
         <v>110100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>112200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>112900</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
       <c r="R76" s="3">
         <v>0</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-49300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,8 +4617,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4434,7 +4633,7 @@
         <v>700</v>
       </c>
       <c r="G83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
@@ -4446,16 +4645,16 @@
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>600</v>
       </c>
       <c r="M83" s="3">
         <v>600</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -4475,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-600</v>
       </c>
       <c r="O89" s="3">
         <v>-600</v>
       </c>
       <c r="P89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,8 +5053,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4889,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,53 +5228,56 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-116200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5057,8 +5287,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5108,8 +5342,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,53 +5546,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>73400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>500</v>
       </c>
       <c r="O100" s="3">
         <v>500</v>
       </c>
       <c r="P100" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q100" s="3">
         <v>117100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5359,8 +5605,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5368,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
@@ -5377,26 +5626,26 @@
         <v>-100</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -5415,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-37500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-100</v>
       </c>
       <c r="O102" s="3">
         <v>-100</v>
       </c>
       <c r="P102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,137 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>6900</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>5700</v>
       </c>
-      <c r="H8" s="3">
-        <v>5400</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>5300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5100</v>
       </c>
       <c r="K8" s="3">
         <v>5100</v>
       </c>
       <c r="L8" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="M8" s="3">
         <v>4800</v>
       </c>
       <c r="N8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="O8" s="3">
         <v>4700</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -805,47 +809,50 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>2100</v>
       </c>
-      <c r="F9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2000</v>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2000</v>
       </c>
       <c r="M9" s="3">
         <v>2000</v>
       </c>
       <c r="N9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O9" s="3">
         <v>2100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,47 +871,50 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>4500</v>
       </c>
-      <c r="F10" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>3700</v>
       </c>
-      <c r="H10" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>3300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2900</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2800</v>
       </c>
       <c r="M10" s="3">
         <v>2800</v>
       </c>
       <c r="N10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O10" s="3">
         <v>2600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,31 +959,32 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>2800</v>
       </c>
-      <c r="F12" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>2400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>2500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3000</v>
       </c>
       <c r="K12" s="3">
         <v>3000</v>
@@ -979,14 +993,14 @@
         <v>3000</v>
       </c>
       <c r="M12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N12" s="3">
         <v>2600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2500</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,47 +1081,50 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>45100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>46100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1123,22 +1143,25 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3">
-        <v>800</v>
-      </c>
       <c r="G15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
@@ -1147,17 +1170,17 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
       <c r="L15" s="3">
+        <v>700</v>
+      </c>
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K17" s="3">
+        <v>13500</v>
+      </c>
+      <c r="L17" s="3">
         <v>11600</v>
       </c>
-      <c r="E17" s="3">
-        <v>11300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>11000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>10800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>11500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>13500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>11600</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4800</v>
       </c>
-      <c r="F18" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <v>-4600</v>
       </c>
-      <c r="H18" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
+      <c r="T18" s="3">
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,50 +1376,51 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-47200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-46200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>38800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1396,53 +1430,56 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-6000</v>
       </c>
-      <c r="F21" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-5200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-4500</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>41000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-45700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,28 +1498,31 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>100</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>100</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1494,7 +1534,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1520,105 +1560,111 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
         <v>-5300</v>
       </c>
-      <c r="H23" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-49300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>600</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="H26" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-49300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9800</v>
       </c>
-      <c r="F27" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
         <v>-5300</v>
       </c>
-      <c r="H27" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-49300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,50 +2118,53 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>400</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
-        <v>300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>47200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>46200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-38800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2104,73 +2174,79 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9800</v>
       </c>
-      <c r="F33" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-5300</v>
       </c>
-      <c r="H33" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-49300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9800</v>
       </c>
-      <c r="F35" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
         <v>-5300</v>
       </c>
-      <c r="H35" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-49300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,56 +2483,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>36400</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>10100</v>
       </c>
-      <c r="F41" s="3">
-        <v>14600</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
         <v>21000</v>
       </c>
-      <c r="H41" s="3">
-        <v>12300</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>20200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46800</v>
-      </c>
-      <c r="M41" s="3">
-        <v>6500</v>
       </c>
       <c r="N41" s="3">
         <v>6500</v>
       </c>
       <c r="O41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2465,34 +2555,34 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>27200</v>
       </c>
-      <c r="F42" s="3">
-        <v>26800</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>26400</v>
       </c>
-      <c r="H42" s="3">
-        <v>37500</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>31500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>50100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>51600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>20200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2515,46 +2605,49 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>5500</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>4200</v>
       </c>
-      <c r="H43" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>3800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
-      </c>
-      <c r="M43" s="3">
-        <v>3200</v>
       </c>
       <c r="N43" s="3">
         <v>3200</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2574,8 +2667,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2606,8 +2702,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2633,37 +2729,40 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4500</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3300</v>
       </c>
       <c r="M45" s="3">
         <v>3300</v>
@@ -2672,87 +2771,93 @@
         <v>3300</v>
       </c>
       <c r="O45" s="3">
-        <v>300</v>
+        <v>3300</v>
       </c>
       <c r="P45" s="3">
         <v>300</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>45300</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
         <v>46100</v>
       </c>
-      <c r="F46" s="3">
-        <v>50200</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
         <v>55400</v>
       </c>
-      <c r="H46" s="3">
-        <v>57700</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>59700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>64700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>68900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>73600</v>
-      </c>
-      <c r="M46" s="3">
-        <v>13000</v>
       </c>
       <c r="N46" s="3">
         <v>13000</v>
       </c>
       <c r="O46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P46" s="3">
         <v>500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2783,23 +2888,23 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>116300</v>
-      </c>
-      <c r="P47" s="3">
-        <v>116200</v>
       </c>
       <c r="Q47" s="3">
         <v>116200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>116200</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2810,46 +2915,49 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>2200</v>
       </c>
       <c r="N48" s="3">
         <v>2200</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -2869,46 +2977,49 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>23500</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3">
         <v>23900</v>
       </c>
-      <c r="F49" s="3">
-        <v>27900</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
         <v>22300</v>
       </c>
-      <c r="H49" s="3">
-        <v>22800</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3">
         <v>23200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24700</v>
-      </c>
-      <c r="M49" s="3">
-        <v>25100</v>
       </c>
       <c r="N49" s="3">
         <v>25100</v>
       </c>
       <c r="O49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,28 +3163,31 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1600</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>1600</v>
       </c>
-      <c r="G52" s="3">
-        <v>1600</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
-        <v>1600</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>1600</v>
@@ -3076,26 +3196,26 @@
         <v>1600</v>
       </c>
       <c r="L52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M52" s="3">
         <v>1700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1600</v>
       </c>
       <c r="N52" s="3">
         <v>1600</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>73300</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>73800</v>
       </c>
-      <c r="F54" s="3">
-        <v>82700</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
         <v>82200</v>
       </c>
-      <c r="H54" s="3">
-        <v>85000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>87700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>92400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>102500</v>
-      </c>
-      <c r="M54" s="3">
-        <v>41800</v>
       </c>
       <c r="N54" s="3">
         <v>41800</v>
       </c>
       <c r="O54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="P54" s="3">
         <v>116800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>116900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,46 +3399,47 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>5700</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3500</v>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>3100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3200</v>
       </c>
       <c r="N57" s="3">
         <v>3200</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -3328,117 +3459,123 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>700</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
-        <v>700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>700</v>
       </c>
       <c r="L58" s="3">
+        <v>700</v>
+      </c>
+      <c r="M58" s="3">
         <v>600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3100</v>
       </c>
       <c r="N58" s="3">
         <v>3100</v>
       </c>
       <c r="O58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>6000</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>11100</v>
       </c>
-      <c r="F59" s="3">
-        <v>5500</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>6400</v>
       </c>
-      <c r="H59" s="3">
-        <v>5600</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>7500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3300</v>
-      </c>
-      <c r="M59" s="3">
-        <v>10700</v>
       </c>
       <c r="N59" s="3">
         <v>10700</v>
       </c>
       <c r="O59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="P59" s="3">
         <v>1700</v>
-      </c>
-      <c r="P59" s="3">
-        <v>100</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3446,105 +3583,111 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>19300</v>
-      </c>
-      <c r="E60" s="3">
-        <v>17300</v>
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F60" s="3">
         <v>17300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>16000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="K60" s="3">
         <v>14500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M60" s="3">
         <v>13700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>14500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>14000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>13700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>17100</v>
       </c>
       <c r="N60" s="3">
         <v>17100</v>
       </c>
       <c r="O60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
-        <v>500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>600</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>200</v>
       </c>
       <c r="L61" s="3">
+        <v>200</v>
+      </c>
+      <c r="M61" s="3">
         <v>300</v>
-      </c>
-      <c r="M61" s="3">
-        <v>400</v>
       </c>
       <c r="N61" s="3">
         <v>400</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3564,8 +3707,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3581,29 +3727,29 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2700</v>
       </c>
       <c r="N62" s="3">
         <v>2700</v>
       </c>
       <c r="O62" s="3">
-        <v>4000</v>
+        <v>2700</v>
       </c>
       <c r="P62" s="3">
         <v>4000</v>
@@ -3611,8 +3757,8 @@
       <c r="Q62" s="3">
         <v>4000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>4000</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>21800</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>18900</v>
       </c>
-      <c r="F66" s="3">
-        <v>19100</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
         <v>17800</v>
       </c>
-      <c r="H66" s="3">
-        <v>16400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>15600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>20100</v>
       </c>
       <c r="N66" s="3">
         <v>20100</v>
       </c>
       <c r="O66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="P66" s="3">
         <v>6700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-211200</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-206700</v>
       </c>
-      <c r="F72" s="3">
-        <v>-196800</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-194100</v>
       </c>
-      <c r="H72" s="3">
-        <v>-188800</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-184200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-180900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-173700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-168000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-118700</v>
       </c>
       <c r="N72" s="3">
         <v>-118700</v>
       </c>
       <c r="O72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="P72" s="3">
         <v>-6200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3200</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
         <v>0</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>51500</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>54900</v>
       </c>
-      <c r="F76" s="3">
-        <v>63600</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>64300</v>
       </c>
-      <c r="H76" s="3">
-        <v>68600</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3">
         <v>72000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>77800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>82900</v>
-      </c>
-      <c r="M76" s="3">
-        <v>21700</v>
       </c>
       <c r="N76" s="3">
         <v>21700</v>
       </c>
       <c r="O76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="P76" s="3">
         <v>110100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>112200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>112900</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9800</v>
       </c>
-      <c r="F81" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
         <v>-5300</v>
       </c>
-      <c r="H81" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-49300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,25 +4816,26 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
-        <v>700</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
@@ -4648,16 +4847,16 @@
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>600</v>
       </c>
       <c r="N83" s="3">
         <v>600</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>300</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-2800</v>
       </c>
-      <c r="H89" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-600</v>
       </c>
       <c r="P89" s="3">
         <v>-600</v>
       </c>
       <c r="Q89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,28 +5274,29 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,56 +5458,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>25900</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>11500</v>
       </c>
-      <c r="H94" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>18100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-116200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5345,8 +5579,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,56 +5792,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>100</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>73400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
-      </c>
-      <c r="O100" s="3">
-        <v>500</v>
       </c>
       <c r="P100" s="3">
         <v>500</v>
       </c>
       <c r="Q100" s="3">
+        <v>500</v>
+      </c>
+      <c r="R100" s="3">
         <v>117100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5608,47 +5854,50 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>26300</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
-        <v>-6500</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>8700</v>
       </c>
-      <c r="H102" s="3">
-        <v>-7900</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>15100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-37500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-100</v>
       </c>
       <c r="P102" s="3">
         <v>-100</v>
       </c>
       <c r="Q102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>CRGO</t>
   </si>
@@ -656,103 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -760,41 +764,41 @@
         <v>7400</v>
       </c>
       <c r="E8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4800</v>
       </c>
       <c r="J8" s="3">
         <v>4800</v>
       </c>
       <c r="K8" s="3">
-        <v>5100</v>
+        <v>4800</v>
       </c>
       <c r="L8" s="3">
         <v>5100</v>
       </c>
       <c r="M8" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="N8" s="3">
         <v>4800</v>
       </c>
       <c r="O8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="P8" s="3">
         <v>4700</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -813,50 +817,53 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2000</v>
       </c>
       <c r="G9" s="3">
         <v>2000</v>
       </c>
       <c r="H9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2000</v>
       </c>
       <c r="J9" s="3">
         <v>2000</v>
       </c>
       <c r="K9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>2000</v>
       </c>
       <c r="N9" s="3">
         <v>2000</v>
       </c>
       <c r="O9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P9" s="3">
         <v>2100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,50 +882,53 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2900</v>
-      </c>
-      <c r="M10" s="3">
-        <v>2800</v>
       </c>
       <c r="N10" s="3">
         <v>2800</v>
       </c>
       <c r="O10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,8 +947,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,34 +974,35 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>3000</v>
       </c>
       <c r="I12" s="3">
         <v>3000</v>
       </c>
       <c r="J12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K12" s="3">
         <v>2600</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3000</v>
       </c>
       <c r="L12" s="3">
         <v>3000</v>
@@ -997,14 +1011,14 @@
         <v>3000</v>
       </c>
       <c r="N12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O12" s="3">
         <v>2600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2500</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,50 +1102,53 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>45100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>46100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>46100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1147,44 +1167,47 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
       </c>
       <c r="M15" s="3">
+        <v>700</v>
+      </c>
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
+      <c r="U18" s="3">
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,53 +1411,54 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-47200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-46200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>38800</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-46200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>38800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1434,14 +1468,17 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1449,41 +1486,41 @@
         <v>-4000</v>
       </c>
       <c r="E21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-6000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>40300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-45700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-45700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1502,19 +1539,22 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1538,7 +1578,7 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1564,70 +1604,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1635,40 +1681,40 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1688,8 +1734,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-49300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-49300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-49300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,53 +2189,56 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>47200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>46200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-38800</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>46200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-38800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2178,76 +2248,82 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-49300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-49300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-49300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-49300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,59 +2571,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E41" s="3">
         <v>20000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46800</v>
-      </c>
-      <c r="N41" s="3">
-        <v>6500</v>
       </c>
       <c r="O41" s="3">
         <v>6500</v>
       </c>
       <c r="P41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,46 +2634,49 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E42" s="3">
         <v>14200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>51600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>20200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>50100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>51600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>20200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2609,49 +2699,52 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>3200</v>
       </c>
       <c r="O43" s="3">
         <v>3200</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2671,8 +2764,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2706,8 +2802,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2733,40 +2829,43 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3300</v>
       </c>
       <c r="J45" s="3">
         <v>3300</v>
       </c>
       <c r="K45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3300</v>
       </c>
       <c r="N45" s="3">
         <v>3300</v>
@@ -2775,90 +2874,96 @@
         <v>3300</v>
       </c>
       <c r="P45" s="3">
-        <v>300</v>
+        <v>3300</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
       </c>
       <c r="T45" s="3">
+        <v>200</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E46" s="3">
         <v>43800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>55400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>68900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>64700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>68900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>73600</v>
-      </c>
-      <c r="N46" s="3">
-        <v>13000</v>
       </c>
       <c r="O46" s="3">
         <v>13000</v>
       </c>
       <c r="P46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q46" s="3">
         <v>500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2892,23 +2997,23 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>116300</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>116200</v>
       </c>
       <c r="R47" s="3">
         <v>116200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>116200</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2919,49 +3024,52 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>2200</v>
       </c>
       <c r="O48" s="3">
         <v>2200</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -2981,49 +3089,52 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E49" s="3">
         <v>23400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>24700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>25100</v>
       </c>
       <c r="O49" s="3">
         <v>25100</v>
       </c>
       <c r="P49" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,13 +3284,16 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E52" s="3">
         <v>1600</v>
@@ -3188,38 +3308,38 @@
         <v>1600</v>
       </c>
       <c r="I52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J52" s="3">
         <v>1700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>1600</v>
       </c>
       <c r="M52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N52" s="3">
         <v>1700</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1600</v>
       </c>
       <c r="O52" s="3">
         <v>1600</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E54" s="3">
         <v>71600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>87700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>102500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>102500</v>
-      </c>
-      <c r="N54" s="3">
-        <v>41800</v>
       </c>
       <c r="O54" s="3">
         <v>41800</v>
       </c>
       <c r="P54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="Q54" s="3">
         <v>116800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>116900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>117000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,49 +3531,50 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>3200</v>
       </c>
       <c r="K57" s="3">
         <v>3200</v>
       </c>
       <c r="L57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>3200</v>
       </c>
       <c r="O57" s="3">
         <v>3200</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3463,123 +3594,129 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>700</v>
       </c>
       <c r="L58" s="3">
         <v>700</v>
       </c>
       <c r="M58" s="3">
+        <v>700</v>
+      </c>
+      <c r="N58" s="3">
         <v>600</v>
-      </c>
-      <c r="N58" s="3">
-        <v>3100</v>
       </c>
       <c r="O58" s="3">
         <v>3100</v>
       </c>
       <c r="P58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>10700</v>
       </c>
       <c r="O59" s="3">
         <v>10700</v>
       </c>
       <c r="P59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>100</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
@@ -3587,111 +3724,117 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E60" s="3">
         <v>20400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13700</v>
-      </c>
-      <c r="N60" s="3">
-        <v>17100</v>
       </c>
       <c r="O60" s="3">
         <v>17100</v>
       </c>
       <c r="P60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>200</v>
       </c>
       <c r="L61" s="3">
         <v>200</v>
       </c>
       <c r="M61" s="3">
+        <v>200</v>
+      </c>
+      <c r="N61" s="3">
         <v>300</v>
-      </c>
-      <c r="N61" s="3">
-        <v>400</v>
       </c>
       <c r="O61" s="3">
         <v>400</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3711,8 +3854,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3725,35 +3871,35 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>4000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4400</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2700</v>
       </c>
       <c r="O62" s="3">
         <v>2700</v>
       </c>
       <c r="P62" s="3">
-        <v>4000</v>
+        <v>2700</v>
       </c>
       <c r="Q62" s="3">
         <v>4000</v>
@@ -3761,8 +3907,8 @@
       <c r="R62" s="3">
         <v>4000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>4000</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E66" s="3">
         <v>22900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19600</v>
-      </c>
-      <c r="N66" s="3">
-        <v>20100</v>
       </c>
       <c r="O66" s="3">
         <v>20100</v>
       </c>
       <c r="P66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="Q66" s="3">
         <v>6700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-224200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-215400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-206700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-194100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-184200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-173700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-168000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-118700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-180900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-173700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-168000</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-118700</v>
       </c>
       <c r="O72" s="3">
         <v>-118700</v>
       </c>
       <c r="P72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3200</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E76" s="3">
         <v>48800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>54900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>77800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>82900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>77800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>82900</v>
-      </c>
-      <c r="N76" s="3">
-        <v>21700</v>
       </c>
       <c r="O76" s="3">
         <v>21700</v>
       </c>
       <c r="P76" s="3">
+        <v>21700</v>
+      </c>
+      <c r="Q76" s="3">
         <v>110100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>112200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>112900</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-49300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-49300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5016,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4827,7 +5026,7 @@
         <v>700</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -4836,31 +5035,31 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>600</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2700</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-600</v>
       </c>
       <c r="Q89" s="3">
         <v>-600</v>
       </c>
       <c r="R89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,17 +5496,18 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,59 +5689,62 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-116200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5524,8 +5754,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5583,8 +5817,8 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,59 +6039,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>73400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>73400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>500</v>
       </c>
       <c r="Q100" s="3">
         <v>500</v>
       </c>
       <c r="R100" s="3">
+        <v>500</v>
+      </c>
+      <c r="S100" s="3">
         <v>117100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5858,50 +6104,53 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-37500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-100</v>
       </c>
       <c r="Q102" s="3">
         <v>-100</v>
       </c>
       <c r="R102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
